--- a/data/trans_bre/POLIPATOLOGIA_Lim_5-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_Lim_5-Estudios-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,03; 12,82</t>
+          <t>6,76; 12,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,68; 15,03</t>
+          <t>8,59; 15,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,62; 18,79</t>
+          <t>10,44; 18,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64,48; 162,22</t>
+          <t>60,86; 157,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,21; 222,81</t>
+          <t>91,5; 229,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,16; 102,51</t>
+          <t>45,6; 102,66</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,52</t>
+          <t>1,27; 3,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,78</t>
+          <t>2,45; 4,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 6,26</t>
+          <t>1,77; 6,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73,46; 359,3</t>
+          <t>75,64; 355,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>114,95; 370,96</t>
+          <t>109,27; 362,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,05; 175,84</t>
+          <t>37,03; 178,34</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 3,45</t>
+          <t>-0,83; 3,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 3,14</t>
+          <t>-1,14; 3,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,19; 7,37</t>
+          <t>3,32; 7,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-53,53; 809,3</t>
+          <t>-48,71; 1296,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-41,81; 289,25</t>
+          <t>-42,49; 294,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>95,83; 432,23</t>
+          <t>84,06; 422,41</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,54; 6,9</t>
+          <t>4,47; 6,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 6,96</t>
+          <t>4,65; 6,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,92; 9,26</t>
+          <t>5,03; 9,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>111,24; 224,2</t>
+          <t>108,21; 224,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>132,09; 260,59</t>
+          <t>128,02; 252,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,36; 165,36</t>
+          <t>73,41; 165,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/POLIPATOLOGIA_Lim_5-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_Lim_5-Estudios-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14,71</t>
+          <t>15,08</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>77,87%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,76; 12,45</t>
+          <t>6,85; 12,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,59; 15,23</t>
+          <t>8,48; 14,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,44; 18,6</t>
+          <t>10,84; 18,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60,86; 157,17</t>
+          <t>61,88; 163,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,5; 229,93</t>
+          <t>91,54; 229,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,6; 102,66</t>
+          <t>48,12; 110,87</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,19</t>
+          <t>4,9</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>93,81%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,53</t>
+          <t>1,26; 3,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,83</t>
+          <t>2,35; 4,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 6,33</t>
+          <t>3,56; 6,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75,64; 355,17</t>
+          <t>75,0; 377,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>109,27; 362,93</t>
+          <t>112,12; 360,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,03; 178,34</t>
+          <t>62,04; 140,28</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,19</t>
+          <t>5,33</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>210,94%</t>
+          <t>217,8%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 3,37</t>
+          <t>-0,85; 3,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,14</t>
+          <t>-1,12; 2,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 7,36</t>
+          <t>3,5; 7,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-48,71; 1296,41</t>
+          <t>-60,94; 769,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-42,49; 294,73</t>
+          <t>-42,53; 263,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>84,06; 422,41</t>
+          <t>98,38; 449,44</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,47</t>
+          <t>8,04</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>112,14%</t>
+          <t>115,05%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,47; 6,86</t>
+          <t>4,45; 6,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,65; 6,92</t>
+          <t>4,74; 7,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,03; 9,19</t>
+          <t>6,88; 9,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108,21; 224,53</t>
+          <t>107,22; 220,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>128,02; 252,65</t>
+          <t>127,83; 255,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,41; 165,99</t>
+          <t>90,17; 145,26</t>
         </is>
       </c>
     </row>
